--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run4/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run4/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,784 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9518,0.0108,0.0144,0.0064</t>
-  </si>
-  <si>
-    <t>0.0074,0.0007,0.0015,0.9955</t>
-  </si>
-  <si>
-    <t>0.6955,0.0158,0.0028,0.3489</t>
-  </si>
-  <si>
-    <t>0.0150,0.0151,0.0016,0.9913</t>
-  </si>
-  <si>
-    <t>0.9978,0.0002,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9955,0.0013,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9909,0.0024,0.0008,0.0017</t>
-  </si>
-  <si>
-    <t>0.9977,0.0009,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9928,0.0030,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.9699,0.0387,0.0012,0.0009</t>
-  </si>
-  <si>
-    <t>0.9953,0.0010,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.7506,0.0698,0.2231,0.0249</t>
-  </si>
-  <si>
-    <t>0.0911,0.1068,0.7743,0.0050</t>
-  </si>
-  <si>
-    <t>0.2849,0.0659,0.7023,0.0025</t>
-  </si>
-  <si>
-    <t>0.0377,0.0364,0.9258,0.0078</t>
-  </si>
-  <si>
-    <t>0.8403,0.0132,0.2369,0.0011</t>
-  </si>
-  <si>
-    <t>0.0025,0.9930,0.0006,0.0009</t>
-  </si>
-  <si>
-    <t>0.0035,0.9901,0.0072,0.0008</t>
-  </si>
-  <si>
-    <t>0.1293,0.8560,0.0075,0.0089</t>
-  </si>
-  <si>
-    <t>0.0033,0.9905,0.0041,0.0017</t>
-  </si>
-  <si>
-    <t>0.0035,0.9895,0.0035,0.0012</t>
-  </si>
-  <si>
-    <t>0.4323,0.0061,0.6667,0.0097</t>
-  </si>
-  <si>
-    <t>0.6774,0.0064,0.4435,0.0019</t>
-  </si>
-  <si>
-    <t>0.0377,0.0074,0.9435,0.0084</t>
-  </si>
-  <si>
-    <t>0.1374,0.0070,0.8904,0.0058</t>
-  </si>
-  <si>
-    <t>0.0327,0.0050,0.9628,0.0032</t>
-  </si>
-  <si>
-    <t>0.2509,0.0021,0.7861,0.0121</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9946,0.0171</t>
-  </si>
-  <si>
-    <t>0.5586,0.5118,0.0274,0.0037</t>
-  </si>
-  <si>
-    <t>0.7821,0.1081,0.1418,0.0066</t>
-  </si>
-  <si>
-    <t>0.0015,0.0058,0.9906,0.0086</t>
-  </si>
-  <si>
-    <t>0.0066,0.9720,0.0409,0.0006</t>
-  </si>
-  <si>
-    <t>0.8118,0.1428,0.0575,0.0197</t>
-  </si>
-  <si>
-    <t>0.6976,0.1312,0.1982,0.0241</t>
-  </si>
-  <si>
-    <t>0.4634,0.5468,0.0011,0.0088</t>
-  </si>
-  <si>
-    <t>0.0377,0.9622,0.0164,0.0007</t>
-  </si>
-  <si>
-    <t>0.0056,0.9266,0.3185,0.0192</t>
-  </si>
-  <si>
-    <t>0.0507,0.0114,0.9426,0.0093</t>
-  </si>
-  <si>
-    <t>0.0454,0.2211,0.9238,0.0020</t>
-  </si>
-  <si>
-    <t>0.0342,0.0133,0.9303,0.0206</t>
-  </si>
-  <si>
-    <t>0.0115,0.6855,0.8985,0.0044</t>
-  </si>
-  <si>
-    <t>0.0169,0.9076,0.1239,0.0015</t>
-  </si>
-  <si>
-    <t>0.0085,0.0302,0.9689,0.0055</t>
-  </si>
-  <si>
-    <t>0.0135,0.5014,0.0022,0.9452</t>
-  </si>
-  <si>
-    <t>0.2512,0.7722,0.0165,0.0061</t>
-  </si>
-  <si>
-    <t>0.0104,0.9663,0.0502,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.9945,0.0105,0.0050</t>
-  </si>
-  <si>
-    <t>0.0327,0.2746,0.9206,0.0100</t>
-  </si>
-  <si>
-    <t>0.0033,0.1823,0.9872,0.0001</t>
-  </si>
-  <si>
-    <t>0.1455,0.0423,0.8255,0.0100</t>
-  </si>
-  <si>
-    <t>0.1264,0.0027,0.9410,0.0003</t>
-  </si>
-  <si>
-    <t>0.0024,0.0027,0.9919,0.0030</t>
-  </si>
-  <si>
-    <t>0.0058,0.1162,0.9625,0.0037</t>
-  </si>
-  <si>
-    <t>0.9063,0.1010,0.0107,0.0046</t>
-  </si>
-  <si>
-    <t>0.9525,0.0056,0.0025,0.0345</t>
-  </si>
-  <si>
-    <t>0.9913,0.0020,0.0004,0.0018</t>
-  </si>
-  <si>
-    <t>0.0008,0.0062,0.9934,0.0147</t>
-  </si>
-  <si>
-    <t>0.9883,0.0051,0.0006,0.0014</t>
-  </si>
-  <si>
-    <t>0.9949,0.0012,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9595,0.0324,0.0151,0.0017</t>
-  </si>
-  <si>
-    <t>0.0013,0.8006,0.9229,0.0021</t>
-  </si>
-  <si>
-    <t>0.0010,0.0143,0.9966,0.0002</t>
-  </si>
-  <si>
-    <t>0.0117,0.0055,0.9844,0.0010</t>
-  </si>
-  <si>
-    <t>0.0002,0.9558,0.9827,0.0001</t>
-  </si>
-  <si>
-    <t>0.0049,0.0032,0.9891,0.0021</t>
-  </si>
-  <si>
-    <t>0.0619,0.9224,0.0092,0.0004</t>
-  </si>
-  <si>
-    <t>0.0075,0.9890,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.6917,0.0131,0.3952,0.0071</t>
-  </si>
-  <si>
-    <t>0.3999,0.3112,0.3693,0.0067</t>
-  </si>
-  <si>
-    <t>0.0241,0.0712,0.9320,0.0055</t>
-  </si>
-  <si>
-    <t>0.0015,0.9571,0.5206,0.0001</t>
-  </si>
-  <si>
-    <t>0.0042,0.8797,0.8255,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.9968,0.0732,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9782,0.9679,0.0000</t>
-  </si>
-  <si>
-    <t>0.0736,0.0038,0.0267,0.9420</t>
-  </si>
-  <si>
-    <t>0.0044,0.0008,0.0006,0.9974</t>
-  </si>
-  <si>
-    <t>0.0157,0.0010,0.0001,0.9956</t>
-  </si>
-  <si>
-    <t>0.0136,0.0036,0.0014,0.9930</t>
-  </si>
-  <si>
-    <t>0.0091,0.0070,0.0029,0.9933</t>
-  </si>
-  <si>
-    <t>0.0036,0.0046,0.0077,0.9946</t>
-  </si>
-  <si>
-    <t>0.0034,0.9457,0.7655,0.0015</t>
-  </si>
-  <si>
-    <t>0.0017,0.8898,0.9141,0.0003</t>
-  </si>
-  <si>
-    <t>0.0339,0.1471,0.8941,0.0044</t>
-  </si>
-  <si>
-    <t>0.0119,0.7403,0.8287,0.0074</t>
-  </si>
-  <si>
-    <t>0.0009,0.9793,0.2896,0.0001</t>
-  </si>
-  <si>
-    <t>0.0042,0.9039,0.6790,0.0012</t>
-  </si>
-  <si>
-    <t>0.9940,0.0039,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9710,0.0360,0.0020,0.0007</t>
-  </si>
-  <si>
-    <t>0.9808,0.0058,0.0008,0.0033</t>
-  </si>
-  <si>
-    <t>0.9902,0.0035,0.0008,0.0013</t>
-  </si>
-  <si>
-    <t>0.9904,0.0026,0.0005,0.0020</t>
-  </si>
-  <si>
-    <t>0.9962,0.0038,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9935,0.0013,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.9813,0.0169,0.0030,0.0008</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9976,0.0004,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9971,0.0004,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9971,0.0003,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9971,0.0005,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9965,0.0007,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9963,0.0008,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9990,0.0000,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.0057,0.0011,0.9892,0.0038</t>
-  </si>
-  <si>
-    <t>0.0115,0.0075,0.9747,0.0020</t>
-  </si>
-  <si>
-    <t>0.7282,0.0131,0.1985,0.0402</t>
-  </si>
-  <si>
-    <t>0.1171,0.0042,0.9336,0.0004</t>
-  </si>
-  <si>
-    <t>0.0148,0.9704,0.0099,0.0020</t>
-  </si>
-  <si>
-    <t>0.0138,0.9762,0.0017,0.0022</t>
-  </si>
-  <si>
-    <t>0.0657,0.9159,0.0024,0.0066</t>
-  </si>
-  <si>
-    <t>0.0744,0.9211,0.0085,0.0028</t>
-  </si>
-  <si>
-    <t>0.0035,0.9887,0.0011,0.0041</t>
-  </si>
-  <si>
-    <t>0.0014,0.9954,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.6818,0.4423,0.0066,0.0016</t>
-  </si>
-  <si>
-    <t>0.2874,0.6195,0.0933,0.0825</t>
-  </si>
-  <si>
-    <t>0.3281,0.0049,0.7618,0.0104</t>
-  </si>
-  <si>
-    <t>0.7590,0.1187,0.0732,0.0113</t>
-  </si>
-  <si>
-    <t>0.6061,0.0582,0.4747,0.0090</t>
-  </si>
-  <si>
-    <t>0.1762,0.2494,0.0503,0.8313</t>
-  </si>
-  <si>
-    <t>0.0039,0.9917,0.0024,0.0009</t>
-  </si>
-  <si>
-    <t>0.0010,0.9964,0.0040,0.0009</t>
-  </si>
-  <si>
-    <t>0.0092,0.9150,0.0243,0.3695</t>
-  </si>
-  <si>
-    <t>0.0028,0.8650,0.8369,0.0015</t>
-  </si>
-  <si>
-    <t>0.0584,0.9555,0.0034,0.0007</t>
-  </si>
-  <si>
-    <t>0.7414,0.2707,0.0290,0.0011</t>
-  </si>
-  <si>
-    <t>0.3001,0.7394,0.0299,0.0052</t>
-  </si>
-  <si>
-    <t>0.9935,0.0023,0.0008,0.0007</t>
-  </si>
-  <si>
-    <t>0.9878,0.0022,0.0007,0.0038</t>
-  </si>
-  <si>
-    <t>0.9863,0.0037,0.0014,0.0032</t>
-  </si>
-  <si>
-    <t>0.9923,0.0017,0.0004,0.0014</t>
-  </si>
-  <si>
-    <t>0.9785,0.0083,0.0026,0.0031</t>
-  </si>
-  <si>
-    <t>0.9773,0.0090,0.0062,0.0026</t>
-  </si>
-  <si>
-    <t>0.9815,0.0015,0.0004,0.0086</t>
-  </si>
-  <si>
-    <t>0.9786,0.0061,0.0040,0.0055</t>
-  </si>
-  <si>
-    <t>0.0118,0.4030,0.9229,0.0007</t>
-  </si>
-  <si>
-    <t>0.0090,0.8772,0.4414,0.0004</t>
-  </si>
-  <si>
-    <t>0.0123,0.5844,0.8521,0.0019</t>
-  </si>
-  <si>
-    <t>0.0227,0.2843,0.8393,0.0006</t>
-  </si>
-  <si>
-    <t>0.8449,0.0228,0.1378,0.0103</t>
-  </si>
-  <si>
-    <t>0.8728,0.0438,0.0462,0.0126</t>
-  </si>
-  <si>
-    <t>0.3614,0.0061,0.8204,0.0010</t>
-  </si>
-  <si>
-    <t>0.7657,0.0447,0.1837,0.0155</t>
-  </si>
-  <si>
-    <t>0.0768,0.0013,0.0010,0.9743</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.0003,0.9996</t>
-  </si>
-  <si>
-    <t>0.0025,0.0010,0.0001,0.9987</t>
-  </si>
-  <si>
-    <t>0.0010,0.0003,0.0010,0.9987</t>
-  </si>
-  <si>
-    <t>0.0071,0.5831,0.7937,0.0042</t>
-  </si>
-  <si>
-    <t>0.9865,0.0036,0.0010,0.0028</t>
-  </si>
-  <si>
-    <t>0.0832,0.9175,0.0035,0.0055</t>
-  </si>
-  <si>
-    <t>0.9887,0.0031,0.0004,0.0022</t>
-  </si>
-  <si>
-    <t>0.8057,0.2185,0.0158,0.0067</t>
-  </si>
-  <si>
-    <t>0.9457,0.0234,0.0212,0.0089</t>
-  </si>
-  <si>
-    <t>0.3785,0.0243,0.0038,0.6842</t>
-  </si>
-  <si>
-    <t>0.9624,0.0226,0.0055,0.0048</t>
-  </si>
-  <si>
-    <t>0.0006,0.2171,0.9849,0.0024</t>
-  </si>
-  <si>
-    <t>0.9470,0.0018,0.0020,0.0407</t>
-  </si>
-  <si>
-    <t>0.9480,0.0037,0.0073,0.0366</t>
-  </si>
-  <si>
-    <t>0.3652,0.6687,0.0074,0.0205</t>
-  </si>
-  <si>
-    <t>0.9783,0.0074,0.0033,0.0011</t>
-  </si>
-  <si>
-    <t>0.9223,0.0409,0.0161,0.0041</t>
-  </si>
-  <si>
-    <t>0.3096,0.5743,0.1542,0.0134</t>
-  </si>
-  <si>
-    <t>0.9194,0.0508,0.0290,0.0016</t>
-  </si>
-  <si>
-    <t>0.9231,0.0809,0.0068,0.0014</t>
-  </si>
-  <si>
-    <t>0.9904,0.0030,0.0020,0.0012</t>
-  </si>
-  <si>
-    <t>0.9842,0.0030,0.0003,0.0041</t>
-  </si>
-  <si>
-    <t>0.9910,0.0023,0.0005,0.0017</t>
-  </si>
-  <si>
-    <t>0.9897,0.0002,0.0001,0.0084</t>
-  </si>
-  <si>
-    <t>0.9903,0.0030,0.0006,0.0016</t>
-  </si>
-  <si>
-    <t>0.9833,0.0107,0.0014,0.0013</t>
-  </si>
-  <si>
-    <t>0.9789,0.0065,0.0009,0.0048</t>
-  </si>
-  <si>
-    <t>0.9926,0.0002,0.0000,0.0060</t>
-  </si>
-  <si>
-    <t>0.5547,0.3502,0.0031,0.0292</t>
-  </si>
-  <si>
-    <t>0.5356,0.5486,0.0133,0.0005</t>
-  </si>
-  <si>
-    <t>0.5111,0.6134,0.0098,0.0014</t>
-  </si>
-  <si>
-    <t>0.0260,0.2574,0.9444,0.0023</t>
-  </si>
-  <si>
-    <t>0.6628,0.4434,0.0029,0.0033</t>
-  </si>
-  <si>
-    <t>0.8816,0.1087,0.0177,0.0114</t>
-  </si>
-  <si>
-    <t>0.9450,0.0810,0.0047,0.0012</t>
-  </si>
-  <si>
-    <t>0.7950,0.2790,0.0060,0.0036</t>
-  </si>
-  <si>
-    <t>0.0001,0.0935,0.9982,0.0001</t>
-  </si>
-  <si>
-    <t>0.9173,0.0551,0.0172,0.0117</t>
-  </si>
-  <si>
-    <t>0.0217,0.0091,0.9791,0.0002</t>
-  </si>
-  <si>
-    <t>0.0098,0.1458,0.9683,0.0009</t>
-  </si>
-  <si>
-    <t>0.2037,0.0354,0.8088,0.0137</t>
-  </si>
-  <si>
-    <t>0.0070,0.5318,0.9476,0.0017</t>
-  </si>
-  <si>
-    <t>0.0267,0.0152,0.9693,0.0005</t>
-  </si>
-  <si>
-    <t>0.0080,0.0041,0.9858,0.0015</t>
-  </si>
-  <si>
-    <t>0.0233,0.0061,0.9832,0.0002</t>
-  </si>
-  <si>
-    <t>0.1380,0.4549,0.4670,0.0120</t>
-  </si>
-  <si>
-    <t>0.2824,0.0150,0.8011,0.0050</t>
-  </si>
-  <si>
-    <t>0.1768,0.1233,0.7080,0.0117</t>
-  </si>
-  <si>
-    <t>0.5370,0.0784,0.4886,0.0141</t>
-  </si>
-  <si>
-    <t>0.3731,0.1177,0.4617,0.0012</t>
-  </si>
-  <si>
-    <t>0.3265,0.3078,0.1527,0.0006</t>
-  </si>
-  <si>
-    <t>0.7903,0.0073,0.1408,0.0339</t>
-  </si>
-  <si>
-    <t>0.2644,0.0183,0.7889,0.0020</t>
-  </si>
-  <si>
-    <t>0.3606,0.7747,0.0041,0.0012</t>
-  </si>
-  <si>
-    <t>0.2916,0.8007,0.0044,0.0021</t>
-  </si>
-  <si>
-    <t>0.9576,0.0665,0.0015,0.0010</t>
-  </si>
-  <si>
-    <t>0.9522,0.0502,0.0061,0.0018</t>
-  </si>
-  <si>
-    <t>0.8526,0.2564,0.0041,0.0007</t>
-  </si>
-  <si>
-    <t>0.7792,0.0100,0.2478,0.0060</t>
-  </si>
-  <si>
-    <t>0.9013,0.0167,0.0591,0.0043</t>
-  </si>
-  <si>
-    <t>0.8137,0.0195,0.0632,0.0513</t>
-  </si>
-  <si>
-    <t>0.4735,0.0967,0.4758,0.0367</t>
-  </si>
-  <si>
-    <t>0.7298,0.0625,0.2308,0.0256</t>
-  </si>
-  <si>
-    <t>0.0206,0.0028,0.9423,0.0756</t>
-  </si>
-  <si>
-    <t>0.0306,0.3340,0.8976,0.0098</t>
-  </si>
-  <si>
-    <t>0.0179,0.0589,0.9534,0.0135</t>
-  </si>
-  <si>
-    <t>0.1233,0.0094,0.8920,0.0058</t>
-  </si>
-  <si>
-    <t>0.0189,0.7362,0.5465,0.0030</t>
-  </si>
-  <si>
-    <t>0.9940,0.0007,0.0002,0.0017</t>
-  </si>
-  <si>
-    <t>0.9876,0.0073,0.0005,0.0011</t>
-  </si>
-  <si>
-    <t>0.9889,0.0010,0.0002,0.0044</t>
-  </si>
-  <si>
-    <t>0.9859,0.0091,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9892,0.0054,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9851,0.0120,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9836,0.0097,0.0003,0.0014</t>
-  </si>
-  <si>
-    <t>0.9878,0.0034,0.0007,0.0023</t>
-  </si>
-  <si>
-    <t>0.3647,0.0047,0.7814,0.0031</t>
-  </si>
-  <si>
-    <t>0.4604,0.1959,0.4181,0.0057</t>
-  </si>
-  <si>
-    <t>0.5605,0.0358,0.3392,0.0990</t>
-  </si>
-  <si>
-    <t>0.1456,0.0146,0.8552,0.0093</t>
-  </si>
-  <si>
-    <t>0.0103,0.3883,0.8672,0.0045</t>
-  </si>
-  <si>
-    <t>0.0331,0.0187,0.9345,0.0014</t>
-  </si>
-  <si>
-    <t>0.0012,0.0065,0.9966,0.0002</t>
-  </si>
-  <si>
-    <t>0.0110,0.6576,0.7161,0.0023</t>
-  </si>
-  <si>
-    <t>0.0009,0.0128,0.9964,0.0004</t>
-  </si>
-  <si>
-    <t>0.0388,0.0254,0.9508,0.0011</t>
-  </si>
-  <si>
-    <t>0.3070,0.0322,0.7647,0.0067</t>
-  </si>
-  <si>
-    <t>0.7260,0.0123,0.2157,0.0245</t>
-  </si>
-  <si>
-    <t>0.8730,0.0048,0.1848,0.0024</t>
-  </si>
-  <si>
-    <t>0.8306,0.0385,0.0987,0.0173</t>
-  </si>
-  <si>
-    <t>0.9846,0.0106,0.0009,0.0008</t>
-  </si>
-  <si>
-    <t>0.9926,0.0028,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.9958,0.0017,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9758,0.0207,0.0027,0.0013</t>
-  </si>
-  <si>
-    <t>0.9927,0.0005,0.0001,0.0030</t>
-  </si>
-  <si>
-    <t>0.9740,0.0136,0.0019,0.0034</t>
-  </si>
-  <si>
-    <t>0.9927,0.0024,0.0004,0.0011</t>
-  </si>
-  <si>
-    <t>0.9933,0.0033,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.0173,0.0471,0.9403,0.0034</t>
-  </si>
-  <si>
-    <t>0.0017,0.0908,0.9864,0.0023</t>
-  </si>
-  <si>
-    <t>0.0084,0.0260,0.9787,0.0044</t>
-  </si>
-  <si>
-    <t>0.0208,0.0024,0.9719,0.0030</t>
-  </si>
-  <si>
-    <t>0.0015,0.0012,0.9948,0.0017</t>
-  </si>
-  <si>
-    <t>0.3139,0.0224,0.6556,0.0521</t>
-  </si>
-  <si>
-    <t>0.0563,0.0242,0.9167,0.0246</t>
-  </si>
-  <si>
-    <t>0.0062,0.0108,0.9550,0.0871</t>
-  </si>
-  <si>
-    <t>0.3464,0.0036,0.0071,0.8034</t>
-  </si>
-  <si>
-    <t>0.0478,0.0649,0.0030,0.9717</t>
-  </si>
-  <si>
-    <t>0.0331,0.0017,0.0006,0.9882</t>
-  </si>
-  <si>
-    <t>0.0021,0.0006,0.0007,0.9981</t>
-  </si>
-  <si>
-    <t>0.0023,0.0000,0.0002,0.9989</t>
-  </si>
-  <si>
-    <t>0.6893,0.0189,0.0078,0.3224</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.7599,0.1452,0.0383,0.0793</t>
+  </si>
+  <si>
+    <t>0.0044,0.0006,0.0299,0.9887</t>
+  </si>
+  <si>
+    <t>0.6232,0.0491,0.0206,0.3905</t>
+  </si>
+  <si>
+    <t>0.0392,0.0054,0.0018,0.9853</t>
+  </si>
+  <si>
+    <t>0.9985,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9955,0.0010,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9751,0.0124,0.0060,0.0032</t>
+  </si>
+  <si>
+    <t>0.9972,0.0015,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9841,0.0041,0.0002,0.0029</t>
+  </si>
+  <si>
+    <t>0.9887,0.0068,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9962,0.0001,0.0000,0.0015</t>
+  </si>
+  <si>
+    <t>0.9982,0.0003,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.7728,0.0548,0.1901,0.0076</t>
+  </si>
+  <si>
+    <t>0.3291,0.1165,0.5198,0.0038</t>
+  </si>
+  <si>
+    <t>0.5877,0.0299,0.5708,0.0008</t>
+  </si>
+  <si>
+    <t>0.0287,0.0099,0.9686,0.0006</t>
+  </si>
+  <si>
+    <t>0.8950,0.0135,0.0798,0.0108</t>
+  </si>
+  <si>
+    <t>0.0007,0.9976,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.0018,0.9951,0.0029,0.0002</t>
+  </si>
+  <si>
+    <t>0.5789,0.5499,0.0084,0.0058</t>
+  </si>
+  <si>
+    <t>0.0153,0.9786,0.0014,0.0024</t>
+  </si>
+  <si>
+    <t>0.0028,0.9928,0.0036,0.0004</t>
+  </si>
+  <si>
+    <t>0.6510,0.0084,0.4439,0.0053</t>
+  </si>
+  <si>
+    <t>0.3296,0.0178,0.6777,0.0130</t>
+  </si>
+  <si>
+    <t>0.0159,0.0023,0.9816,0.0009</t>
+  </si>
+  <si>
+    <t>0.0028,0.0071,0.9829,0.0109</t>
+  </si>
+  <si>
+    <t>0.2331,0.0016,0.8702,0.0022</t>
+  </si>
+  <si>
+    <t>0.2013,0.0055,0.8749,0.0021</t>
+  </si>
+  <si>
+    <t>0.0094,0.0020,0.9880,0.0015</t>
+  </si>
+  <si>
+    <t>0.9177,0.1011,0.0120,0.0016</t>
+  </si>
+  <si>
+    <t>0.8289,0.0810,0.1158,0.0141</t>
+  </si>
+  <si>
+    <t>0.0007,0.0057,0.9954,0.0033</t>
+  </si>
+  <si>
+    <t>0.0448,0.8831,0.1068,0.0003</t>
+  </si>
+  <si>
+    <t>0.8203,0.0384,0.1202,0.0270</t>
+  </si>
+  <si>
+    <t>0.8309,0.1034,0.0705,0.0111</t>
+  </si>
+  <si>
+    <t>0.7364,0.3012,0.0233,0.0059</t>
+  </si>
+  <si>
+    <t>0.0087,0.9868,0.0171,0.0006</t>
+  </si>
+  <si>
+    <t>0.0211,0.9214,0.2414,0.0125</t>
+  </si>
+  <si>
+    <t>0.0798,0.0419,0.8556,0.0469</t>
+  </si>
+  <si>
+    <t>0.0434,0.0547,0.9429,0.0067</t>
+  </si>
+  <si>
+    <t>0.0567,0.0072,0.9195,0.0189</t>
+  </si>
+  <si>
+    <t>0.0777,0.0135,0.9323,0.0019</t>
+  </si>
+  <si>
+    <t>0.0087,0.9540,0.0809,0.0022</t>
+  </si>
+  <si>
+    <t>0.0462,0.0472,0.9247,0.0058</t>
+  </si>
+  <si>
+    <t>0.0072,0.5563,0.0004,0.9391</t>
+  </si>
+  <si>
+    <t>0.0004,0.9963,0.0004,0.0082</t>
+  </si>
+  <si>
+    <t>0.0197,0.9518,0.1415,0.0009</t>
+  </si>
+  <si>
+    <t>0.0008,0.9952,0.1058,0.0002</t>
+  </si>
+  <si>
+    <t>0.0036,0.1360,0.9805,0.0029</t>
+  </si>
+  <si>
+    <t>0.0051,0.1967,0.9807,0.0003</t>
+  </si>
+  <si>
+    <t>0.1112,0.0054,0.9189,0.0034</t>
+  </si>
+  <si>
+    <t>0.0288,0.0055,0.9648,0.0044</t>
+  </si>
+  <si>
+    <t>0.0557,0.0039,0.9518,0.0044</t>
+  </si>
+  <si>
+    <t>0.0114,0.0204,0.9597,0.0121</t>
+  </si>
+  <si>
+    <t>0.9477,0.0516,0.0105,0.0014</t>
+  </si>
+  <si>
+    <t>0.9673,0.0167,0.0072,0.0040</t>
+  </si>
+  <si>
+    <t>0.9584,0.0219,0.0135,0.0044</t>
+  </si>
+  <si>
+    <t>0.0005,0.0107,0.9963,0.0047</t>
+  </si>
+  <si>
+    <t>0.9904,0.0062,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9917,0.0022,0.0012,0.0013</t>
+  </si>
+  <si>
+    <t>0.9704,0.0234,0.0042,0.0016</t>
+  </si>
+  <si>
+    <t>0.0040,0.4390,0.9569,0.0022</t>
+  </si>
+  <si>
+    <t>0.0051,0.0185,0.9906,0.0004</t>
+  </si>
+  <si>
+    <t>0.0049,0.0206,0.9771,0.0167</t>
+  </si>
+  <si>
+    <t>0.0003,0.9762,0.9353,0.0002</t>
+  </si>
+  <si>
+    <t>0.0097,0.0026,0.9823,0.0041</t>
+  </si>
+  <si>
+    <t>0.0313,0.9384,0.0291,0.0003</t>
+  </si>
+  <si>
+    <t>0.0081,0.9875,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9244,0.0176,0.0756,0.0024</t>
+  </si>
+  <si>
+    <t>0.7950,0.1279,0.1023,0.0071</t>
+  </si>
+  <si>
+    <t>0.0077,0.0225,0.9682,0.0234</t>
+  </si>
+  <si>
+    <t>0.0047,0.6804,0.9176,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.8504,0.9584,0.0001</t>
+  </si>
+  <si>
+    <t>0.0020,0.9809,0.2440,0.0007</t>
+  </si>
+  <si>
+    <t>0.0009,0.9401,0.8705,0.0004</t>
+  </si>
+  <si>
+    <t>0.0169,0.0004,0.0118,0.9814</t>
+  </si>
+  <si>
+    <t>0.0045,0.0009,0.0000,0.9984</t>
+  </si>
+  <si>
+    <t>0.0064,0.0046,0.0004,0.9965</t>
+  </si>
+  <si>
+    <t>0.0025,0.0030,0.0346,0.9896</t>
+  </si>
+  <si>
+    <t>0.0067,0.0008,0.0045,0.9934</t>
+  </si>
+  <si>
+    <t>0.0023,0.0115,0.0003,0.9980</t>
+  </si>
+  <si>
+    <t>0.0029,0.9734,0.2542,0.0009</t>
+  </si>
+  <si>
+    <t>0.0011,0.7179,0.9782,0.0001</t>
+  </si>
+  <si>
+    <t>0.0195,0.3483,0.8803,0.0008</t>
+  </si>
+  <si>
+    <t>0.0039,0.2781,0.9801,0.0008</t>
+  </si>
+  <si>
+    <t>0.0006,0.9890,0.4753,0.0001</t>
+  </si>
+  <si>
+    <t>0.0203,0.5854,0.7821,0.0024</t>
+  </si>
+  <si>
+    <t>0.9948,0.0022,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9484,0.0883,0.0028,0.0010</t>
+  </si>
+  <si>
+    <t>0.9832,0.0212,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9932,0.0007,0.0003,0.0020</t>
+  </si>
+  <si>
+    <t>0.9778,0.0186,0.0007,0.0011</t>
+  </si>
+  <si>
+    <t>0.9952,0.0018,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9895,0.0052,0.0005,0.0010</t>
+  </si>
+  <si>
+    <t>0.9516,0.0457,0.0064,0.0034</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9960,0.0018,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9972,0.0001,0.0000,0.0017</t>
+  </si>
+  <si>
+    <t>0.9973,0.0004,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9983,0.0002,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9941,0.0006,0.0004,0.0019</t>
+  </si>
+  <si>
+    <t>0.9972,0.0003,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9968,0.0002,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.0085,0.0075,0.9850,0.0046</t>
+  </si>
+  <si>
+    <t>0.1337,0.1071,0.7871,0.0122</t>
+  </si>
+  <si>
+    <t>0.5100,0.0327,0.5375,0.0157</t>
+  </si>
+  <si>
+    <t>0.1704,0.0091,0.8878,0.0009</t>
+  </si>
+  <si>
+    <t>0.0160,0.9693,0.0008,0.0055</t>
+  </si>
+  <si>
+    <t>0.0042,0.9867,0.0042,0.0040</t>
+  </si>
+  <si>
+    <t>0.0072,0.9839,0.0012,0.0026</t>
+  </si>
+  <si>
+    <t>0.0678,0.9134,0.0035,0.0117</t>
+  </si>
+  <si>
+    <t>0.0053,0.9855,0.0005,0.0059</t>
+  </si>
+  <si>
+    <t>0.0040,0.9908,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.4491,0.6653,0.0067,0.0021</t>
+  </si>
+  <si>
+    <t>0.7540,0.0595,0.1120,0.0830</t>
+  </si>
+  <si>
+    <t>0.1575,0.0067,0.8725,0.0089</t>
+  </si>
+  <si>
+    <t>0.6355,0.0702,0.3326,0.0150</t>
+  </si>
+  <si>
+    <t>0.5967,0.0571,0.3800,0.0134</t>
+  </si>
+  <si>
+    <t>0.5866,0.0512,0.0139,0.4469</t>
+  </si>
+  <si>
+    <t>0.0035,0.9910,0.0067,0.0010</t>
+  </si>
+  <si>
+    <t>0.0004,0.9968,0.0022,0.0019</t>
+  </si>
+  <si>
+    <t>0.0126,0.9136,0.0140,0.1825</t>
+  </si>
+  <si>
+    <t>0.0002,0.8651,0.9816,0.0001</t>
+  </si>
+  <si>
+    <t>0.0347,0.9670,0.0130,0.0006</t>
+  </si>
+  <si>
+    <t>0.7460,0.2552,0.0353,0.0090</t>
+  </si>
+  <si>
+    <t>0.1045,0.9004,0.0119,0.0020</t>
+  </si>
+  <si>
+    <t>0.9887,0.0046,0.0015,0.0013</t>
+  </si>
+  <si>
+    <t>0.9876,0.0013,0.0003,0.0058</t>
+  </si>
+  <si>
+    <t>0.9845,0.0057,0.0016,0.0026</t>
+  </si>
+  <si>
+    <t>0.9838,0.0018,0.0010,0.0068</t>
+  </si>
+  <si>
+    <t>0.9847,0.0033,0.0003,0.0047</t>
+  </si>
+  <si>
+    <t>0.9767,0.0131,0.0057,0.0021</t>
+  </si>
+  <si>
+    <t>0.9873,0.0031,0.0008,0.0034</t>
+  </si>
+  <si>
+    <t>0.9915,0.0019,0.0006,0.0016</t>
+  </si>
+  <si>
+    <t>0.0008,0.8962,0.9631,0.0001</t>
+  </si>
+  <si>
+    <t>0.0087,0.6493,0.8448,0.0003</t>
+  </si>
+  <si>
+    <t>0.0067,0.7166,0.8247,0.0012</t>
+  </si>
+  <si>
+    <t>0.0463,0.0493,0.9456,0.0025</t>
+  </si>
+  <si>
+    <t>0.7495,0.1012,0.0947,0.0511</t>
+  </si>
+  <si>
+    <t>0.8194,0.1026,0.0479,0.0117</t>
+  </si>
+  <si>
+    <t>0.0820,0.0027,0.9429,0.0037</t>
+  </si>
+  <si>
+    <t>0.8156,0.0908,0.0194,0.0167</t>
+  </si>
+  <si>
+    <t>0.0895,0.0019,0.0011,0.9696</t>
+  </si>
+  <si>
+    <t>0.0009,0.0005,0.0003,0.9992</t>
+  </si>
+  <si>
+    <t>0.0001,0.1575,0.0007,0.9986</t>
+  </si>
+  <si>
+    <t>0.0026,0.0010,0.0006,0.9981</t>
+  </si>
+  <si>
+    <t>0.0055,0.7357,0.8655,0.0032</t>
+  </si>
+  <si>
+    <t>0.9846,0.0060,0.0033,0.0025</t>
+  </si>
+  <si>
+    <t>0.1354,0.8792,0.0051,0.0126</t>
+  </si>
+  <si>
+    <t>0.9681,0.0187,0.0043,0.0029</t>
+  </si>
+  <si>
+    <t>0.6934,0.3840,0.0081,0.0089</t>
+  </si>
+  <si>
+    <t>0.9623,0.0136,0.0099,0.0076</t>
+  </si>
+  <si>
+    <t>0.7682,0.0083,0.0148,0.2292</t>
+  </si>
+  <si>
+    <t>0.9816,0.0075,0.0029,0.0032</t>
+  </si>
+  <si>
+    <t>0.0002,0.0840,0.9919,0.0050</t>
+  </si>
+  <si>
+    <t>0.8810,0.0004,0.0027,0.1186</t>
+  </si>
+  <si>
+    <t>0.9209,0.0152,0.0023,0.0463</t>
+  </si>
+  <si>
+    <t>0.4176,0.6577,0.0123,0.0041</t>
+  </si>
+  <si>
+    <t>0.9430,0.0458,0.0099,0.0018</t>
+  </si>
+  <si>
+    <t>0.9689,0.0158,0.0078,0.0005</t>
+  </si>
+  <si>
+    <t>0.1051,0.8353,0.0304,0.1131</t>
+  </si>
+  <si>
+    <t>0.8543,0.0596,0.0884,0.0046</t>
+  </si>
+  <si>
+    <t>0.9263,0.0442,0.0193,0.0031</t>
+  </si>
+  <si>
+    <t>0.9918,0.0009,0.0001,0.0018</t>
+  </si>
+  <si>
+    <t>0.9900,0.0019,0.0013,0.0019</t>
+  </si>
+  <si>
+    <t>0.9908,0.0024,0.0005,0.0014</t>
+  </si>
+  <si>
+    <t>0.9926,0.0003,0.0001,0.0047</t>
+  </si>
+  <si>
+    <t>0.9786,0.0113,0.0033,0.0028</t>
+  </si>
+  <si>
+    <t>0.9620,0.0323,0.0043,0.0025</t>
+  </si>
+  <si>
+    <t>0.9838,0.0082,0.0022,0.0013</t>
+  </si>
+  <si>
+    <t>0.9830,0.0057,0.0013,0.0049</t>
+  </si>
+  <si>
+    <t>0.9212,0.0869,0.0028,0.0040</t>
+  </si>
+  <si>
+    <t>0.8507,0.1883,0.0194,0.0016</t>
+  </si>
+  <si>
+    <t>0.4828,0.5501,0.0222,0.0037</t>
+  </si>
+  <si>
+    <t>0.0249,0.8000,0.5749,0.0015</t>
+  </si>
+  <si>
+    <t>0.8344,0.2202,0.0038,0.0034</t>
+  </si>
+  <si>
+    <t>0.9774,0.0174,0.0017,0.0011</t>
+  </si>
+  <si>
+    <t>0.8908,0.1474,0.0095,0.0031</t>
+  </si>
+  <si>
+    <t>0.9450,0.0450,0.0019,0.0049</t>
+  </si>
+  <si>
+    <t>0.0006,0.2156,0.9933,0.0002</t>
+  </si>
+  <si>
+    <t>0.9419,0.0554,0.0076,0.0030</t>
+  </si>
+  <si>
+    <t>0.0046,0.0124,0.9890,0.0004</t>
+  </si>
+  <si>
+    <t>0.0032,0.0253,0.9872,0.0041</t>
+  </si>
+  <si>
+    <t>0.0367,0.0015,0.9699,0.0018</t>
+  </si>
+  <si>
+    <t>0.0132,0.0313,0.9616,0.0077</t>
+  </si>
+  <si>
+    <t>0.0498,0.0317,0.9268,0.0014</t>
+  </si>
+  <si>
+    <t>0.0026,0.0187,0.9895,0.0003</t>
+  </si>
+  <si>
+    <t>0.0104,0.0156,0.9770,0.0018</t>
+  </si>
+  <si>
+    <t>0.5641,0.0326,0.4986,0.0108</t>
+  </si>
+  <si>
+    <t>0.1728,0.0169,0.8486,0.0085</t>
+  </si>
+  <si>
+    <t>0.5878,0.1824,0.2118,0.0773</t>
+  </si>
+  <si>
+    <t>0.5407,0.2068,0.2035,0.0026</t>
+  </si>
+  <si>
+    <t>0.2224,0.6239,0.1433,0.0042</t>
+  </si>
+  <si>
+    <t>0.2568,0.4340,0.1857,0.0037</t>
+  </si>
+  <si>
+    <t>0.5658,0.2302,0.1917,0.0925</t>
+  </si>
+  <si>
+    <t>0.5251,0.2369,0.2535,0.0218</t>
+  </si>
+  <si>
+    <t>0.8180,0.3118,0.0034,0.0007</t>
+  </si>
+  <si>
+    <t>0.7921,0.3186,0.0012,0.0016</t>
+  </si>
+  <si>
+    <t>0.8744,0.1478,0.0166,0.0014</t>
+  </si>
+  <si>
+    <t>0.9414,0.0720,0.0076,0.0010</t>
+  </si>
+  <si>
+    <t>0.9476,0.0838,0.0025,0.0009</t>
+  </si>
+  <si>
+    <t>0.8005,0.0256,0.1229,0.0220</t>
+  </si>
+  <si>
+    <t>0.9440,0.0057,0.0450,0.0020</t>
+  </si>
+  <si>
+    <t>0.8971,0.0152,0.0464,0.0127</t>
+  </si>
+  <si>
+    <t>0.1003,0.0969,0.8077,0.0054</t>
+  </si>
+  <si>
+    <t>0.4958,0.0223,0.5617,0.0177</t>
+  </si>
+  <si>
+    <t>0.0205,0.0217,0.9353,0.0415</t>
+  </si>
+  <si>
+    <t>0.1389,0.0334,0.8582,0.0073</t>
+  </si>
+  <si>
+    <t>0.0343,0.1078,0.9267,0.0165</t>
+  </si>
+  <si>
+    <t>0.0567,0.0197,0.9361,0.0056</t>
+  </si>
+  <si>
+    <t>0.0311,0.7109,0.5032,0.0217</t>
+  </si>
+  <si>
+    <t>0.9872,0.0006,0.0001,0.0067</t>
+  </si>
+  <si>
+    <t>0.9752,0.0150,0.0023,0.0026</t>
+  </si>
+  <si>
+    <t>0.9798,0.0117,0.0025,0.0024</t>
+  </si>
+  <si>
+    <t>0.9767,0.0219,0.0007,0.0012</t>
+  </si>
+  <si>
+    <t>0.9884,0.0019,0.0010,0.0040</t>
+  </si>
+  <si>
+    <t>0.9921,0.0018,0.0006,0.0016</t>
+  </si>
+  <si>
+    <t>0.9864,0.0088,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.9866,0.0066,0.0013,0.0015</t>
+  </si>
+  <si>
+    <t>0.0775,0.0068,0.9306,0.0101</t>
+  </si>
+  <si>
+    <t>0.4136,0.1207,0.5952,0.0112</t>
+  </si>
+  <si>
+    <t>0.8844,0.0373,0.0437,0.0283</t>
+  </si>
+  <si>
+    <t>0.0072,0.0061,0.9882,0.0004</t>
+  </si>
+  <si>
+    <t>0.0020,0.0134,0.9885,0.0022</t>
+  </si>
+  <si>
+    <t>0.0174,0.1240,0.9421,0.0003</t>
+  </si>
+  <si>
+    <t>0.0022,0.0054,0.9938,0.0012</t>
+  </si>
+  <si>
+    <t>0.0645,0.1398,0.8225,0.0013</t>
+  </si>
+  <si>
+    <t>0.0114,0.0378,0.9647,0.0094</t>
+  </si>
+  <si>
+    <t>0.0364,0.0107,0.9492,0.0066</t>
+  </si>
+  <si>
+    <t>0.3326,0.0931,0.6017,0.0274</t>
+  </si>
+  <si>
+    <t>0.8872,0.0076,0.1327,0.0020</t>
+  </si>
+  <si>
+    <t>0.6833,0.0363,0.2979,0.0505</t>
+  </si>
+  <si>
+    <t>0.6289,0.2005,0.1834,0.0092</t>
+  </si>
+  <si>
+    <t>0.9869,0.0048,0.0008,0.0020</t>
+  </si>
+  <si>
+    <t>0.9943,0.0038,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9950,0.0017,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9743,0.0198,0.0019,0.0019</t>
+  </si>
+  <si>
+    <t>0.9872,0.0014,0.0002,0.0054</t>
+  </si>
+  <si>
+    <t>0.9875,0.0098,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9952,0.0004,0.0000,0.0010</t>
+  </si>
+  <si>
+    <t>0.9938,0.0016,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.0287,0.0337,0.9262,0.0075</t>
+  </si>
+  <si>
+    <t>0.0029,0.0283,0.9876,0.0006</t>
+  </si>
+  <si>
+    <t>0.0873,0.0895,0.8573,0.0279</t>
+  </si>
+  <si>
+    <t>0.0367,0.0183,0.9398,0.0033</t>
+  </si>
+  <si>
+    <t>0.0162,0.0126,0.9640,0.0154</t>
+  </si>
+  <si>
+    <t>0.5860,0.1011,0.3353,0.0462</t>
+  </si>
+  <si>
+    <t>0.0545,0.0217,0.9233,0.0184</t>
+  </si>
+  <si>
+    <t>0.0076,0.1273,0.8571,0.0910</t>
+  </si>
+  <si>
+    <t>0.4639,0.0097,0.0169,0.6936</t>
+  </si>
+  <si>
+    <t>0.0159,0.0151,0.0009,0.9913</t>
+  </si>
+  <si>
+    <t>0.0024,0.0021,0.0011,0.9979</t>
+  </si>
+  <si>
+    <t>0.0033,0.0004,0.0000,0.9989</t>
+  </si>
+  <si>
+    <t>0.0017,0.0010,0.0001,0.9991</t>
+  </si>
+  <si>
+    <t>0.5452,0.0080,0.0054,0.5965</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1971,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1985,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1999,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2013,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2027,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2041,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2055,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2069,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2083,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2097,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2111,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2125,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2139,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2153,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,10 +2164,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2181,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2195,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2209,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2223,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,10 +2234,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2251,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2265,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2276,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2290,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2307,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2321,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2335,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2349,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2363,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2374,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2391,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2405,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2419,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2433,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2447,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2458,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2475,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2489,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2503,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2517,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2531,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,10 +2542,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2559,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2573,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2584,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2601,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2615,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2629,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2643,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2657,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2671,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2685,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2699,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2713,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2727,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2741,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2755,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2769,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2783,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2797,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2811,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,10 +2822,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2839,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2853,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2867,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2881,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2895,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2909,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2923,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2937,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2951,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2965,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2979,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2993,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3007,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3021,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3035,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3049,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3063,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3077,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3091,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,10 +3102,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3119,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3133,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,10 +3144,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3161,7 @@
         <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3175,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3189,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3203,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3217,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3231,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3245,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3259,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3273,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3287,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3301,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3315,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3329,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3343,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3357,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3371,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3385,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3399,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3413,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3427,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,10 +3438,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3455,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3469,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3483,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3497,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3511,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3525,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3539,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3550,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,10 +3564,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3581,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3595,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,7 +3609,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3620,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3637,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3651,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3665,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3679,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3693,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3707,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3721,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3735,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3749,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3763,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3777,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3791,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3805,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3819,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3833,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,10 +3844,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3858,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3875,7 @@
         <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3889,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3903,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3917,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3931,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3945,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3959,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3973,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3987,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +4001,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4015,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4029,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4043,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4057,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4071,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4085,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,10 +4096,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4113,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4127,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4141,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4155,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4169,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4183,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4197,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4211,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4225,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4239,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4253,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4267,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4281,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4295,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4309,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4323,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4337,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4351,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4365,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4376,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4393,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4404,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4421,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4435,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4449,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4463,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4477,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4491,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4505,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4519,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4533,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,10 +4544,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4561,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4575,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4589,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4603,7 @@
         <v>259</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4617,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4628,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,7 +4645,7 @@
         <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4656,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4670,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4687,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4698,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,10 +4712,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,10 +4726,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4743,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4757,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4771,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4785,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4799,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4813,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4824,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,10 +4838,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4855,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4869,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4883,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4897,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4911,7 @@
         <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4925,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4939,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4953,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4967,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4981,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4995,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5009,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5023,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5037,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5048,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5065,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5079,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5093,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5107,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5121,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,10 +5132,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5149,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5163,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5177,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5191,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5205,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5219,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5233,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5247,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5261,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5275,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5289,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5303,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5317,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5331,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5345,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5359,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5373,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5387,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5401,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5412,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5429,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5443,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5457,7 @@
         <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5471,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5485,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5499,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5513,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5524,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
